--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/region-de-los-lagos.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/region-de-los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2306-639-CM26</t>
+          <t>1071775-2-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>MUEBLES ANDROMEDA DOS SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.285.439-0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,43 +569,43 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>20053.4</v>
+        <v>27796.04</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2852-804-CM26</t>
+          <t>1393093-26-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.235.755-0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,43 +630,43 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6536.01</v>
+        <v>21799.95</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>507428-878-CM26</t>
+          <t>4180-30-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>MUEBLES ANDROMEDA DOS SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
+          <t>77.285.439-0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,28 +691,28 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>55525</v>
+        <v>7712.21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2852-848-CM26</t>
+          <t>696954-10-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,28 +752,28 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8793.07</v>
+        <v>23451.74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1071775-128-CM26</t>
+          <t>2324-533-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,6 +813,1714 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
+        <v>26749.32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1057536-2100-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>61.607.700-7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>COMERCIAL VYB SPA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>76.583.479-1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>12583.78</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1057536-2102-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>61.607.700-7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>8943.030000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1071775-34-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>70.772.100-6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>37145.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2852-325-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Ortopedic</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>77.765.630-9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>10478.15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1224953-263-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>71.420.700-8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CORP MUNICIP ANCUD PARA LA EDUCAC SALUD</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SOC MUEBLES SANTA ANA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>77.624.270-5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>9368.59</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2181-114-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>10562.28</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1393093-437-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.981.360-K</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>76.235.755-0</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>19235.52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2332-645-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>77.749.210-1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>8394.299999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>507428-3037-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61.979.210-6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>10083.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>507428-3111-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>61.979.210-6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>7160.27</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>507428-3112-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.979.210-6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>7160.27</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2324-926-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>21629.88</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1787-42-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>60.804.018-8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>OFISILLAS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.855.435-8</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>13618.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2328-725-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>11345.98</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1071775-78-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>70.772.100-6</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>6525.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>507428-3246-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.979.210-6</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>41836.08</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2324-1125-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>6970.69</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2852-696-CM25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>77.043.435-1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>14433.4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1079639-744-CM25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>61.979.300-5</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>28134.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1180842-38-CM25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>61.979.210-6</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>92.999.000-5</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>499470.96</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1057922-139-CM25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61.607.600-0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OSORNO</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>MUEBLES EASTON LIMITADA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>79.526.830-8</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>111889.13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1057922-138-CM25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>61.607.600-0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OSORNO</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>MUEBLES EASTON LIMITADA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>79.526.830-8</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>131578.76</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4180-152-CM25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>61.979.300-5</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>25899.08</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2306-639-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>20053.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2852-804-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>6536.01</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>507428-878-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>61.979.210-6</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>77.749.210-1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>55525</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2852-848-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>8793.07</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1071775-128-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>70.772.100-6</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
         <v>12738.66</v>
       </c>
     </row>
